--- a/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C91F754-8039-4893-923C-728F720AC348}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E961CB5E-4A78-4E06-9B4B-4CB27400C193}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F230580F-3D72-4EDF-9566-EB348E660DD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{415C986A-4125-4454-BBE9-64574AD28EC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE17604-1348-41AE-AD01-6854321CE3F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E35C98-C7DC-4102-94DB-878AFDB2D6A1}"/>
 </file>